--- a/Italian Serie A/Raw/25_26.xlsx
+++ b/Italian Serie A/Raw/25_26.xlsx
@@ -648,132 +648,132 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>476</v>
+        <v>583</v>
       </c>
       <c r="L2" t="n">
+        <v>23</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" t="n">
         <v>16</v>
       </c>
-      <c r="M2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S2" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="T2" t="n">
-        <v>386</v>
+        <v>468</v>
       </c>
       <c r="U2" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="V2" t="n">
-        <v>83.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>43</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>453</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>2</v>
       </c>
-      <c r="Y2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>62</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>722</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="AN2" t="n">
-        <v>637</v>
+        <v>346</v>
       </c>
       <c r="AO2" t="n">
-        <v>566</v>
+        <v>232</v>
       </c>
       <c r="AP2" t="n">
-        <v>88.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -784,132 +784,132 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="H3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>476</v>
+      </c>
+      <c r="L3" t="n">
         <v>16</v>
       </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>583</v>
-      </c>
-      <c r="L3" t="n">
-        <v>23</v>
-      </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
+        <v>42</v>
+      </c>
+      <c r="T3" t="n">
+        <v>386</v>
+      </c>
+      <c r="U3" t="n">
+        <v>322</v>
+      </c>
+      <c r="V3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
         <v>62</v>
       </c>
-      <c r="T3" t="n">
-        <v>468</v>
-      </c>
-      <c r="U3" t="n">
-        <v>349</v>
-      </c>
-      <c r="V3" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
+      <c r="AB3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>722</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AK3" t="n">
         <v>7</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>43</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>453</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>18</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>28</v>
-      </c>
       <c r="AM3" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="AN3" t="n">
-        <v>346</v>
+        <v>637</v>
       </c>
       <c r="AO3" t="n">
-        <v>232</v>
+        <v>566</v>
       </c>
       <c r="AP3" t="n">
-        <v>67.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -920,132 +920,132 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>51</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>552</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S4" t="n">
+        <v>68</v>
+      </c>
+      <c r="T4" t="n">
+        <v>444</v>
+      </c>
+      <c r="U4" t="n">
+        <v>358</v>
+      </c>
+      <c r="V4" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>517</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>64</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K4" t="n">
-        <v>779</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>13</v>
-      </c>
-      <c r="O4" t="n">
-        <v>22</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>28</v>
-      </c>
-      <c r="S4" t="n">
-        <v>58</v>
-      </c>
-      <c r="T4" t="n">
-        <v>665</v>
-      </c>
-      <c r="U4" t="n">
-        <v>592</v>
-      </c>
-      <c r="V4" t="n">
-        <v>89</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Cremonese</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AH4" t="n">
         <v>14</v>
       </c>
-      <c r="AC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AI4" t="n">
         <v>16</v>
       </c>
-      <c r="AE4" t="n">
-        <v>494</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>37</v>
-      </c>
       <c r="AJ4" t="n">
         <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="AO4" t="n">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="AP4" t="n">
-        <v>79.3</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="5">
@@ -1056,132 +1056,132 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K5" t="n">
+        <v>779</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>58</v>
+      </c>
+      <c r="T5" t="n">
+        <v>665</v>
+      </c>
+      <c r="U5" t="n">
+        <v>592</v>
+      </c>
+      <c r="V5" t="n">
+        <v>89</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB5" t="n">
         <v>14</v>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>51</v>
-      </c>
-      <c r="H5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="AC5" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>552</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="AD5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>494</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>37</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
         <v>13</v>
       </c>
-      <c r="M5" t="n">
-        <v>9</v>
-      </c>
-      <c r="N5" t="n">
-        <v>12</v>
-      </c>
-      <c r="O5" t="n">
-        <v>17</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>16</v>
-      </c>
-      <c r="S5" t="n">
-        <v>68</v>
-      </c>
-      <c r="T5" t="n">
-        <v>444</v>
-      </c>
-      <c r="U5" t="n">
-        <v>358</v>
-      </c>
-      <c r="V5" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>49</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AL5" t="n">
         <v>14</v>
       </c>
-      <c r="AE5" t="n">
-        <v>517</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>23</v>
-      </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="AN5" t="n">
-        <v>434</v>
+        <v>376</v>
       </c>
       <c r="AO5" t="n">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="AP5" t="n">
-        <v>75.8</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="6">
@@ -2552,132 +2552,132 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="H16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>756</v>
+        <v>441</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
         <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="S16" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="T16" t="n">
-        <v>686</v>
+        <v>299</v>
       </c>
       <c r="U16" t="n">
-        <v>587</v>
+        <v>197</v>
       </c>
       <c r="V16" t="n">
-        <v>85.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
-        <v>446</v>
+        <v>750</v>
       </c>
       <c r="AF16" t="n">
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH16" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AL16" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AM16" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="AN16" t="n">
-        <v>327</v>
+        <v>640</v>
       </c>
       <c r="AO16" t="n">
-        <v>264</v>
+        <v>522</v>
       </c>
       <c r="AP16" t="n">
-        <v>80.7</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -2688,132 +2688,132 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>68</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13</v>
+      </c>
+      <c r="J17" t="n">
+        <v>42</v>
+      </c>
+      <c r="K17" t="n">
+        <v>756</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
         <v>7</v>
       </c>
-      <c r="F17" t="n">
+      <c r="N17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P17" t="n">
         <v>3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>32</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>11</v>
-      </c>
-      <c r="K17" t="n">
-        <v>441</v>
-      </c>
-      <c r="L17" t="n">
-        <v>22</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11</v>
-      </c>
-      <c r="N17" t="n">
-        <v>17</v>
-      </c>
-      <c r="O17" t="n">
-        <v>40</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="S17" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="T17" t="n">
-        <v>299</v>
+        <v>686</v>
       </c>
       <c r="U17" t="n">
-        <v>197</v>
+        <v>587</v>
       </c>
       <c r="V17" t="n">
-        <v>65.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="AB17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
-        <v>750</v>
+        <v>446</v>
       </c>
       <c r="AF17" t="n">
         <v>16</v>
       </c>
       <c r="AG17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AI17" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="AN17" t="n">
-        <v>640</v>
+        <v>327</v>
       </c>
       <c r="AO17" t="n">
-        <v>522</v>
+        <v>264</v>
       </c>
       <c r="AP17" t="n">
-        <v>81.59999999999999</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="18">
@@ -2824,132 +2824,132 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>530</v>
+        <v>424</v>
       </c>
       <c r="L18" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
         <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>14</v>
+      </c>
+      <c r="R18" t="n">
+        <v>18</v>
+      </c>
+      <c r="S18" t="n">
+        <v>56</v>
+      </c>
+      <c r="T18" t="n">
+        <v>336</v>
+      </c>
+      <c r="U18" t="n">
+        <v>251</v>
+      </c>
+      <c r="V18" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>23</v>
-      </c>
-      <c r="S18" t="n">
-        <v>58</v>
-      </c>
-      <c r="T18" t="n">
-        <v>391</v>
-      </c>
-      <c r="U18" t="n">
-        <v>283</v>
-      </c>
-      <c r="V18" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
         <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AB18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>494</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="n">
         <v>14</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>632</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>15</v>
       </c>
       <c r="AI18" t="n">
         <v>23</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AL18" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="AM18" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="AN18" t="n">
-        <v>499</v>
+        <v>397</v>
       </c>
       <c r="AO18" t="n">
-        <v>391</v>
+        <v>324</v>
       </c>
       <c r="AP18" t="n">
-        <v>78.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2960,132 +2960,132 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>530</v>
+      </c>
+      <c r="L19" t="n">
         <v>21</v>
-      </c>
-      <c r="I19" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>18</v>
-      </c>
-      <c r="K19" t="n">
-        <v>424</v>
-      </c>
-      <c r="L19" t="n">
-        <v>7</v>
       </c>
       <c r="M19" t="n">
         <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T19" t="n">
-        <v>336</v>
+        <v>391</v>
       </c>
       <c r="U19" t="n">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="V19" t="n">
-        <v>74.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
         <v>3</v>
       </c>
       <c r="AA19" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AB19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>494</v>
+        <v>632</v>
       </c>
       <c r="AF19" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AH19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI19" t="n">
         <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AL19" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="AM19" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="AN19" t="n">
-        <v>397</v>
+        <v>499</v>
       </c>
       <c r="AO19" t="n">
-        <v>324</v>
+        <v>391</v>
       </c>
       <c r="AP19" t="n">
-        <v>81.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3096,132 +3096,132 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>70</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" t="n">
+        <v>842</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>14</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="G20" t="n">
-        <v>67</v>
-      </c>
-      <c r="H20" t="n">
+      <c r="R20" t="n">
         <v>17</v>
       </c>
-      <c r="I20" t="n">
-        <v>13</v>
-      </c>
-      <c r="J20" t="n">
-        <v>37</v>
-      </c>
-      <c r="K20" t="n">
-        <v>657</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="S20" t="n">
+        <v>63</v>
+      </c>
+      <c r="T20" t="n">
+        <v>745</v>
+      </c>
+      <c r="U20" t="n">
+        <v>668</v>
+      </c>
+      <c r="V20" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>12</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20</v>
-      </c>
-      <c r="O20" t="n">
-        <v>19</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>82</v>
-      </c>
-      <c r="T20" t="n">
-        <v>567</v>
-      </c>
-      <c r="U20" t="n">
-        <v>459</v>
-      </c>
-      <c r="V20" t="n">
-        <v>81</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="X20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>9</v>
       </c>
       <c r="Z20" t="n">
         <v>4</v>
       </c>
       <c r="AA20" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AB20" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>437</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL20" t="n">
         <v>12</v>
       </c>
-      <c r="AE20" t="n">
-        <v>403</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>21</v>
-      </c>
       <c r="AM20" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="AN20" t="n">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="AO20" t="n">
-        <v>197</v>
+        <v>253</v>
       </c>
       <c r="AP20" t="n">
-        <v>70.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3232,132 +3232,132 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H21" t="n">
+        <v>17</v>
+      </c>
+      <c r="I21" t="n">
+        <v>13</v>
+      </c>
+      <c r="J21" t="n">
+        <v>37</v>
+      </c>
+      <c r="K21" t="n">
+        <v>657</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20</v>
+      </c>
+      <c r="O21" t="n">
+        <v>19</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
         <v>8</v>
       </c>
-      <c r="I21" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>20</v>
-      </c>
-      <c r="K21" t="n">
-        <v>842</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="R21" t="n">
+        <v>25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>82</v>
+      </c>
+      <c r="T21" t="n">
+        <v>567</v>
+      </c>
+      <c r="U21" t="n">
+        <v>459</v>
+      </c>
+      <c r="V21" t="n">
+        <v>81</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="n">
         <v>9</v>
-      </c>
-      <c r="M21" t="n">
-        <v>14</v>
-      </c>
-      <c r="N21" t="n">
-        <v>13</v>
-      </c>
-      <c r="O21" t="n">
-        <v>7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>17</v>
-      </c>
-      <c r="S21" t="n">
-        <v>63</v>
-      </c>
-      <c r="T21" t="n">
-        <v>745</v>
-      </c>
-      <c r="U21" t="n">
-        <v>668</v>
-      </c>
-      <c r="V21" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Hellas Verona</t>
-        </is>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>12</v>
       </c>
       <c r="Z21" t="n">
         <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AB21" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
-        <v>437</v>
+        <v>403</v>
       </c>
       <c r="AF21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH21" t="n">
         <v>20</v>
       </c>
-      <c r="AG21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>4</v>
-      </c>
       <c r="AI21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL21" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="AN21" t="n">
-        <v>324</v>
+        <v>279</v>
       </c>
       <c r="AO21" t="n">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="AP21" t="n">
-        <v>78.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Italian Serie A/Raw/25_26.xlsx
+++ b/Italian Serie A/Raw/25_26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP21"/>
+  <dimension ref="A1:AP31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3358,6 +3358,1366 @@
       </c>
       <c r="AP21" t="n">
         <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>51</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13</v>
+      </c>
+      <c r="K22" t="n">
+        <v>549</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" t="n">
+        <v>15</v>
+      </c>
+      <c r="O22" t="n">
+        <v>33</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10</v>
+      </c>
+      <c r="R22" t="n">
+        <v>21</v>
+      </c>
+      <c r="S22" t="n">
+        <v>67</v>
+      </c>
+      <c r="T22" t="n">
+        <v>439</v>
+      </c>
+      <c r="U22" t="n">
+        <v>344</v>
+      </c>
+      <c r="V22" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>49</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>539</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>66</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>418</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>325</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>41</v>
+      </c>
+      <c r="H23" t="n">
+        <v>14</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" t="n">
+        <v>502</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>39</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>14</v>
+      </c>
+      <c r="S23" t="n">
+        <v>47</v>
+      </c>
+      <c r="T23" t="n">
+        <v>388</v>
+      </c>
+      <c r="U23" t="n">
+        <v>317</v>
+      </c>
+      <c r="V23" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Internazionale</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>59</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>654</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>557</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>479</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>19</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>53</v>
+      </c>
+      <c r="H24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23</v>
+      </c>
+      <c r="K24" t="n">
+        <v>580</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16</v>
+      </c>
+      <c r="O24" t="n">
+        <v>16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>14</v>
+      </c>
+      <c r="S24" t="n">
+        <v>58</v>
+      </c>
+      <c r="T24" t="n">
+        <v>496</v>
+      </c>
+      <c r="U24" t="n">
+        <v>393</v>
+      </c>
+      <c r="V24" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>47</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>561</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>56</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>446</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>360</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>22</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>72</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>31</v>
+      </c>
+      <c r="K25" t="n">
+        <v>751</v>
+      </c>
+      <c r="L25" t="n">
+        <v>12</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>17</v>
+      </c>
+      <c r="O25" t="n">
+        <v>12</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>19</v>
+      </c>
+      <c r="S25" t="n">
+        <v>56</v>
+      </c>
+      <c r="T25" t="n">
+        <v>647</v>
+      </c>
+      <c r="U25" t="n">
+        <v>561</v>
+      </c>
+      <c r="V25" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>386</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>43</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>63</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>253</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>175</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>56</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>23</v>
+      </c>
+      <c r="K26" t="n">
+        <v>600</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14</v>
+      </c>
+      <c r="M26" t="n">
+        <v>6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>14</v>
+      </c>
+      <c r="O26" t="n">
+        <v>20</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>14</v>
+      </c>
+      <c r="S26" t="n">
+        <v>44</v>
+      </c>
+      <c r="T26" t="n">
+        <v>499</v>
+      </c>
+      <c r="U26" t="n">
+        <v>408</v>
+      </c>
+      <c r="V26" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>503</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>61</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>390</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>304</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>51</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>29</v>
+      </c>
+      <c r="K27" t="n">
+        <v>547</v>
+      </c>
+      <c r="L27" t="n">
+        <v>14</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20</v>
+      </c>
+      <c r="O27" t="n">
+        <v>24</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" t="n">
+        <v>62</v>
+      </c>
+      <c r="T27" t="n">
+        <v>434</v>
+      </c>
+      <c r="U27" t="n">
+        <v>341</v>
+      </c>
+      <c r="V27" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>49</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>531</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>72</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>416</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>322</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>77.40000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>41</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" t="n">
+        <v>570</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20</v>
+      </c>
+      <c r="M28" t="n">
+        <v>12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>13</v>
+      </c>
+      <c r="O28" t="n">
+        <v>32</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>18</v>
+      </c>
+      <c r="S28" t="n">
+        <v>62</v>
+      </c>
+      <c r="T28" t="n">
+        <v>447</v>
+      </c>
+      <c r="U28" t="n">
+        <v>375</v>
+      </c>
+      <c r="V28" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>59</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>722</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>53</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>637</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>539</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>84.59999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>40</v>
+      </c>
+      <c r="H29" t="n">
+        <v>17</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>14</v>
+      </c>
+      <c r="K29" t="n">
+        <v>480</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>24</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>18</v>
+      </c>
+      <c r="S29" t="n">
+        <v>51</v>
+      </c>
+      <c r="T29" t="n">
+        <v>372</v>
+      </c>
+      <c r="U29" t="n">
+        <v>302</v>
+      </c>
+      <c r="V29" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>645</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>62</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>559</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>474</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>47</v>
+      </c>
+      <c r="H30" t="n">
+        <v>18</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" t="n">
+        <v>23</v>
+      </c>
+      <c r="K30" t="n">
+        <v>564</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11</v>
+      </c>
+      <c r="M30" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" t="n">
+        <v>16</v>
+      </c>
+      <c r="O30" t="n">
+        <v>24</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>15</v>
+      </c>
+      <c r="S30" t="n">
+        <v>63</v>
+      </c>
+      <c r="T30" t="n">
+        <v>458</v>
+      </c>
+      <c r="U30" t="n">
+        <v>353</v>
+      </c>
+      <c r="V30" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>53</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>630</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>37</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>62</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>526</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>426</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>53</v>
+      </c>
+      <c r="H31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>630</v>
+      </c>
+      <c r="L31" t="n">
+        <v>17</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>15</v>
+      </c>
+      <c r="O31" t="n">
+        <v>26</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>32</v>
+      </c>
+      <c r="S31" t="n">
+        <v>52</v>
+      </c>
+      <c r="T31" t="n">
+        <v>493</v>
+      </c>
+      <c r="U31" t="n">
+        <v>411</v>
+      </c>
+      <c r="V31" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>47</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>570</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>59</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>432</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>340</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>78.7</v>
       </c>
     </row>
   </sheetData>
